--- a/docs/Product_Backlog.xlsx
+++ b/docs/Product_Backlog.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java项目\EBU6304-Group17\docs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0E093B-1ACC-48DA-A053-EFE4EDE76171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="12080"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Backlog" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="226">
   <si>
     <t>Story ID</t>
   </si>
@@ -278,530 +284,547 @@
     <t>As a TA, I want to upload a resume in plain text / Word format so that the course organizer can get a more complete picture of my abilities.</t>
   </si>
   <si>
+    <t>Store the file path and do not store the file content directly</t>
+  </si>
+  <si>
+    <t>P1-004</t>
+  </si>
+  <si>
+    <t>Please check the details of the application record</t>
+  </si>
+  <si>
+    <t>As a TA, I want to see the full information on the application record so that I can understand the details of the application.</t>
+  </si>
+  <si>
+    <t>1. TAs can click on the application record to enter the details page
+2. The details page displays the job details, application time, reviewer, and review opinions (if any)
+3. The information display is complete and clear</t>
+  </si>
+  <si>
+    <t>P1-005</t>
+  </si>
+  <si>
+    <t>Editor posted jobs</t>
+  </si>
+  <si>
+    <t>As a MO, I want to edit the information for unclosed and unqualified positions so that I can adjust my hiring needs.</t>
+  </si>
+  <si>
+    <t>1. Only positions that have not been closed and have not been applied for by applicants can be edited</t>
+  </si>
+  <si>
+    <t>P1-006</t>
+  </si>
+  <si>
+    <t>TAs are screened with multiple conditions</t>
+  </si>
+  <si>
+    <t>As a MO, I want to screen TAs by major, availability, etc., so that I can quickly find TAs who meet the requirements.</t>
+  </si>
+  <si>
+    <t>1. The TA list page provides a filter input box
+2. Support screening by major, available working hours, and basic skills
+3. After filtering, the page will update in real time to show qualified TAs</t>
+  </si>
+  <si>
+    <t>P1-007</t>
+  </si>
+  <si>
+    <t>Review applicant applications in bulk</t>
+  </si>
+  <si>
+    <t>As a MO, I want to bulk tag the application status of multiple TAs so that I can improve the review process.</t>
+  </si>
+  <si>
+    <t>1. MO can tick multiple applications from the list of TAs
+2. You can select "Passed" or "Rejected" in batches for the checked applications.
+3. After the batch operation, the status of all selected applications is updated synchronously</t>
+  </si>
+  <si>
+    <t>P1-008</t>
+  </si>
+  <si>
+    <t>Statistics of this account</t>
+  </si>
+  <si>
+    <t>As a MO, I want to see core data for all positions I post so that I can understand the progress of hiring.</t>
+  </si>
+  <si>
+    <t>1. MO can enter the job statistics page
+2. Display the status of the posted position (published/removed/closed), the number of applicants, and the number of passes
+3. Accurate and real-time data statistics</t>
+  </si>
+  <si>
+    <t>P1-009</t>
+  </si>
+  <si>
+    <t>Global post view</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to see all MOs and TAs' personal information so that I can stay on top of the college-wide recruitment progress.</t>
+  </si>
+  <si>
+    <t>1. Administrators can enter the global view list (all users can be viewed)
+2. Display all information of the user, including personal information, TA: application information, MO: application received, etc</t>
+  </si>
+  <si>
+    <t>P1-010</t>
+  </si>
+  <si>
+    <t>Basic account management</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to reset the MO/TA's password or delete an invalid so that I can maintain account security.</t>
+  </si>
+  <si>
+    <t>1. Administrators can reset the account password of any user
+2. Invalid / expired accounts can be deleted
+3. The account status will be updated synchronously after the operation</t>
+  </si>
+  <si>
+    <t>P1-011</t>
+  </si>
+  <si>
+    <t>Paginated display list</t>
+  </si>
+  <si>
+    <t>As a TA / MO / Admin, I want to see pagination when there is too much list data so that I can improve the browsing experience.</t>
+  </si>
+  <si>
+    <t>1. Job list, applicant list, and application record list are paginated
+2. Each page displays a fixed amount of data and supports page turning operations
+3. Pagination navigation is clear and easy to use</t>
+  </si>
+  <si>
+    <t>P1-012</t>
+  </si>
+  <si>
+    <t>Key operation logs</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to record key actions and be able to view logs so that I can trace back to the history of operations.</t>
+  </si>
+  <si>
+    <t>P1-013</t>
+  </si>
+  <si>
+    <t>View individual application history</t>
+  </si>
+  <si>
+    <t>As a TA, I want to sift through all my application records by time so that I can review my application history.</t>
+  </si>
+  <si>
+    <t>1. The application record page supports filtering by time
+2. Display all application records (including withdrawn and unsuccessful)
+3. The list is updated in real time after filtering</t>
+  </si>
+  <si>
+    <t>P2-001</t>
+  </si>
+  <si>
+    <t>Collect the intended position</t>
+  </si>
+  <si>
+    <t>As a TA, I want to save the positions I am interested in so that I can quickly view and apply for them later.</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>1. TAs can click the Favorite button on the job list/details page
+2. Favorite positions are displayed separately on the collection list page
+3. You can cancel your collection</t>
+  </si>
+  <si>
+    <t>P2-002</t>
+  </si>
+  <si>
+    <t>Local alerts on application status</t>
+  </si>
+  <si>
+    <t>As a TA, I want to be alerted when my application status changes so that I can stay up to date with the outcome of my application.</t>
+  </si>
+  <si>
+    <t>1. If the application status changes after logging in, a pop-up message will appear
+2. The prompt content includes the job title and status change results
+3. Prompts can be turned off</t>
+  </si>
+  <si>
+    <t>Local prompts, no SMS/email push</t>
+  </si>
+  <si>
+    <t>P2-003</t>
+  </si>
+  <si>
+    <t>File information export</t>
+  </si>
+  <si>
+    <t>As a TA, I want to export my file information to JSON format so that I can backup offline.</t>
+  </si>
+  <si>
+    <t>1. TAs can click the export button on the profile page
+2. The export file is in JSON format and contains all the archive information
+3. The exported file can be opened and viewed normally</t>
+  </si>
+  <si>
+    <t>Whether to choose JSON format is to be discussed</t>
+  </si>
+  <si>
+    <t>P2-004</t>
+  </si>
+  <si>
+    <t>Set job skill requirements</t>
+  </si>
+  <si>
+    <t>As a MO, I want to add specific skill requirements when posting a job so that I can match hiring needs procisely.</t>
+  </si>
+  <si>
+    <t>1. You can add a skill requirement field to the job posting page
+2. Skill requirements can be selected or entered
+3. Skill requirements are displayed on the job details page</t>
+  </si>
+  <si>
+    <t>P2-005</t>
+  </si>
+  <si>
+    <t>Add review comments</t>
+  </si>
+  <si>
+    <t>As a MO, I want to fill out a comment at the time of review so that I can explain the reason for the review to the TA.</t>
+  </si>
+  <si>
+    <t>1. You can enter text comments during the review
+2. Comments are synchronized to the applicant's application record details page
+3. There is a limit to the length of the comment (e.g. up to 200 words).</t>
+  </si>
+  <si>
+    <t>P2-006</t>
+  </si>
+  <si>
+    <t>The job cut-off time will be automatically removed from the shelves</t>
+  </si>
+  <si>
+    <t>As a MO, I want positions to be automatically removed when the deadline is reached so that I don't receive late applications.</t>
+  </si>
+  <si>
+    <t>1. Positions that have reached the application deadline will be automatically removed
+2. After removal, it will be hidden from the public list and new applications cannot be submitted
+3. Submitted applications can still be reviewed</t>
+  </si>
+  <si>
+    <t>P2-007</t>
+  </si>
+  <si>
+    <t>View the TA Job Fundamentals information</t>
+  </si>
+  <si>
+    <t>As a MO, I want to look at TAs' past teaching assistant experiences so that it can help me assist in review decisions.</t>
+  </si>
+  <si>
+    <t>1. TA profiles include past employment fields
+2. The MO can view this information at the time of the review
+3. Clear information presentation</t>
+  </si>
+  <si>
+    <t>P2-008</t>
+  </si>
+  <si>
+    <t>Workload threshold alerts</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to set TA workload thresholds so that I can be alerted when TA is overloaded.</t>
+  </si>
+  <si>
+    <t>1. Administrators can set thresholds (e.g. up to 3 positions in a single semester)
+2. When the number of TA positions approaches/exceeds the threshold, the system will give a text warning
+3. Alerts are displayed on the Workload page</t>
+  </si>
+  <si>
+    <t>P2-009</t>
+  </si>
+  <si>
+    <t>Statistics of recruitment data of the whole hospital</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to count the recruitment data of the whole college so that I can assist the college management decision-making.</t>
+  </si>
+  <si>
+    <t>1. Statistics on the recruitment completion rate, TA job distribution, and recruitment progress of each MO for each course/activity
+2. Present in a table
+3. Accurate and real-time data statistics</t>
+  </si>
+  <si>
+    <t>P2-010</t>
+  </si>
+  <si>
+    <t>Global data export</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to export the core data of the whole hospital to CSV format so that it can be analysed offline.</t>
+  </si>
+  <si>
+    <t>1. Administrators can export job information, TA job information, and recruitment statistics
+2. Export the file in CSV format
+3. The exported file can be opened and viewed normally</t>
+  </si>
+  <si>
+    <t>Export format TBD</t>
+  </si>
+  <si>
+    <t>P2-011</t>
+  </si>
+  <si>
+    <t>Basic control of operation permissions</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to restrict the MO from only operating the posts I post so that I can ensure data security.</t>
+  </si>
+  <si>
+    <t>1. MO can only view/operate the posts posted by the MO
+2. It is prohibited to view/review applicants for other MO positions across accounts
+3. Permission verification is performed before operation</t>
+  </si>
+  <si>
+    <t>P2-012</t>
+  </si>
+  <si>
+    <t>Manually backup and restore data</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to manually back up and restore system data so that data loss is prevented.</t>
+  </si>
+  <si>
+    <t>1. Administrators can back up all system data (users, positions, application records)
+2. The backup file can be restored to the system
+3. There are clear prompts for backup/restore operations</t>
+  </si>
+  <si>
+    <t>P2-013</t>
+  </si>
+  <si>
+    <t>Interface interaction optimization</t>
+  </si>
+  <si>
+    <t>As a TA / MO / Admin, I want to use a more user-friendly interface so that it can improve the user experience.</t>
+  </si>
+  <si>
+    <t>1. Improve the interface navigation, pop-up prompts, and operation button layout
+2. The interface complies with the medium-fidelity prototype standard
+3. Smoother operation process</t>
+  </si>
+  <si>
+    <t>P2-014</t>
+  </si>
+  <si>
+    <t>Bilingual interface in Chinese and English</t>
+  </si>
+  <si>
+    <t>As a TA / MO / Admin, I want to switch between Chinese and English interfaces so that it can adapt to international usage scenarios.</t>
+  </si>
+  <si>
+    <t>1. The system supports switching between Chinese and English interfaces
+2. The core text is bilingual
+3. The interface is updated in real time after switching</t>
+  </si>
+  <si>
+    <t>P2-015</t>
+  </si>
+  <si>
+    <t>Job time reminder</t>
+  </si>
+  <si>
+    <t>As a TA, I want to see a deadline reminder when I check a position so that I can apply in time.</t>
+  </si>
+  <si>
+    <t>1. Positions marked with "Coming soon" &lt; 24 hours from the deadline
+2. Closed positions marked as "Not Applicable"
+3. The reminder sign is clearly visible</t>
+  </si>
+  <si>
+    <t>P2-016</t>
+  </si>
+  <si>
+    <t>Export the list of TAs</t>
+  </si>
+  <si>
+    <t>As a MO, I want to export the applicant information for this position in Excel format so that it can be viewed and statisticed offline offline.</t>
+  </si>
+  <si>
+    <t>1. MO can be clicked on the export button on the applicant list page
+2. The export file is in Excel format and contains the TA's core information
+3. The exported file can be opened and viewed normally</t>
+  </si>
+  <si>
+    <t>P3-001</t>
+  </si>
+  <si>
+    <t>Tips on the matching degree of personal skills and positions</t>
+  </si>
+  <si>
+    <t>As a TA, I want to see a score on how well my skills match the position so that it can assist in job selection.</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>1. Job details page display match score (percentage)
+2. Scoring is calculated based on the TA's skills and job skills
+3. The scoring logic is explainable</t>
+  </si>
+  <si>
+    <t>AI value-added functions, optionally implemented</t>
+  </si>
+  <si>
+    <t>P3-002</t>
+  </si>
+  <si>
+    <t>Skill shortcomings identification tips</t>
+  </si>
+  <si>
+    <t>As a TA, I want to see my skills shortcomings and suggestions for improvement after applying, so that I can improve my abilities in a targeted manner.</t>
+  </si>
+  <si>
+    <t>1. After applying, the system compares the job requirements and points out the missing skills
+2. Give suggestions for basic improvement
+3. The prompt content is clear and easy to understand</t>
+  </si>
+  <si>
+    <t>P3-003</t>
+  </si>
+  <si>
+    <t>Intelligent screening of TA skills</t>
+  </si>
+  <si>
+    <t>As a MO, I want the system to automatically screen and prioritize high-match TAs so that it can improve screening efficiency.</t>
+  </si>
+  <si>
+    <t>1. The list of TAs is sorted by match, and high matching is prioritized
+2. The matching degree is calculated based on the job skill requirements
+3. Manually adjust the sorting</t>
+  </si>
+  <si>
+    <t>P3-004</t>
+  </si>
+  <si>
+    <t>Resume keyword extraction</t>
+  </si>
+  <si>
+    <t>As a MO, I want the system to automatically extract resume core keywords so that I can quickly understand TA competencies.</t>
+  </si>
+  <si>
+    <t>1. The system extracts key words such as core skills and work experience from the resume
+2. Keywords are displayed on the applicant's information page
+3. The extraction results can be manually verified</t>
+  </si>
+  <si>
+    <t>P3-005</t>
+  </si>
+  <si>
+    <t>TA workload equalization recommendation</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to get recommendations for optimizing TA assignments so that it can balance my workload.</t>
+  </si>
+  <si>
+    <t>1. The system gives an allocation recommendation based on the current TA load
+2. Suggestions can be viewed and modified manually
+3. Suggest logic that is explainable</t>
+  </si>
+  <si>
+    <t>P3-006</t>
+  </si>
+  <si>
+    <t>Intelligent statistics of recruitment demand</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to get reference recommendations for the number of TA recruitments for each course/activity to assist in planning.</t>
+  </si>
+  <si>
+    <t>1. Give a reference to the number of recruits based on past data
+2. References can be adjusted manually
+3. Statistical logic is explainable</t>
+  </si>
+  <si>
+    <t>P3-007</t>
+  </si>
+  <si>
+    <t>AI matching logic is configurable</t>
+  </si>
+  <si>
+    <t>As a Admin, I want to adjust the weight of job skill matching so that I can make the matching results more relevant to my actual needs.</t>
+  </si>
+  <si>
+    <t>1. Weights such as professional skills and work experience can be configured
+2. The matching calculation is updated in real time after configuration
+3. The configuration interface is clear and easy to use</t>
+  </si>
+  <si>
+    <t>P3-008</t>
+  </si>
+  <si>
+    <t>AI results are manually verified</t>
+  </si>
+  <si>
+    <t>As a system user, I want to validate AI-generated results so that I can avoid logical errors.</t>
+  </si>
+  <si>
+    <t>1. All AI-generated results support human viewing
+2. AI results can be modified manually
+3. The modified result overlays the AI-generated content</t>
+  </si>
+  <si>
+    <t>Uncertain</t>
+  </si>
+  <si>
+    <t>Core data persistence</t>
+  </si>
+  <si>
+    <t>As a system developer, I want to add and delete user files, job information, and application records, and store them persistently to ensure that data is not lost.</t>
+  </si>
+  <si>
+    <t>1. All user files, job information, and application records can be added, deleted, modified, and checked
+2. The data is stored in JSON format
+3. Data reading and writing without abnormalities</t>
+  </si>
+  <si>
+    <t>1. Record the posting of positions, submitting applications, reviewing applications, account logins, etc
+2. The logs are stored as text files
+3. Administrators can view the log contents</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>1. TAs can upload resume files on the profile page
 2. The system stores the resume file path to the file
 3. MO can view the content of the resume uploaded by the TA</t>
-  </si>
-  <si>
-    <t>Store the file path and do not store the file content directly</t>
-  </si>
-  <si>
-    <t>P1-004</t>
-  </si>
-  <si>
-    <t>Please check the details of the application record</t>
-  </si>
-  <si>
-    <t>As a TA, I want to see the full information on the application record so that I can understand the details of the application.</t>
-  </si>
-  <si>
-    <t>1. TAs can click on the application record to enter the details page
-2. The details page displays the job details, application time, reviewer, and review opinions (if any)
-3. The information display is complete and clear</t>
-  </si>
-  <si>
-    <t>P1-005</t>
-  </si>
-  <si>
-    <t>Editor posted jobs</t>
-  </si>
-  <si>
-    <t>As a MO, I want to edit the information for unclosed and unqualified positions so that I can adjust my hiring needs.</t>
-  </si>
-  <si>
-    <t>1. Only positions that have not been closed and have not been applied for by applicants can be edited</t>
-  </si>
-  <si>
-    <t>P1-006</t>
-  </si>
-  <si>
-    <t>TAs are screened with multiple conditions</t>
-  </si>
-  <si>
-    <t>As a MO, I want to screen TAs by major, availability, etc., so that I can quickly find TAs who meet the requirements.</t>
-  </si>
-  <si>
-    <t>1. The TA list page provides a filter input box
-2. Support screening by major, available working hours, and basic skills
-3. After filtering, the page will update in real time to show qualified TAs</t>
-  </si>
-  <si>
-    <t>P1-007</t>
-  </si>
-  <si>
-    <t>Review applicant applications in bulk</t>
-  </si>
-  <si>
-    <t>As a MO, I want to bulk tag the application status of multiple TAs so that I can improve the review process.</t>
-  </si>
-  <si>
-    <t>1. MO can tick multiple applications from the list of TAs
-2. You can select "Passed" or "Rejected" in batches for the checked applications.
-3. After the batch operation, the status of all selected applications is updated synchronously</t>
-  </si>
-  <si>
-    <t>P1-008</t>
-  </si>
-  <si>
-    <t>Statistics of this account</t>
-  </si>
-  <si>
-    <t>As a MO, I want to see core data for all positions I post so that I can understand the progress of hiring.</t>
-  </si>
-  <si>
-    <t>1. MO can enter the job statistics page
-2. Display the status of the posted position (published/removed/closed), the number of applicants, and the number of passes
-3. Accurate and real-time data statistics</t>
-  </si>
-  <si>
-    <t>P1-009</t>
-  </si>
-  <si>
-    <t>Global post view</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to see all MOs and TAs' personal information so that I can stay on top of the college-wide recruitment progress.</t>
-  </si>
-  <si>
-    <t>1. Administrators can enter the global view list (all users can be viewed)
-2. Display all information of the user, including personal information, TA: application information, MO: application received, etc</t>
-  </si>
-  <si>
-    <t>P1-010</t>
-  </si>
-  <si>
-    <t>Basic account management</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to reset the MO/TA's password or delete an invalid so that I can maintain account security.</t>
-  </si>
-  <si>
-    <t>1. Administrators can reset the account password of any user
-2. Invalid / expired accounts can be deleted
-3. The account status will be updated synchronously after the operation</t>
-  </si>
-  <si>
-    <t>P1-011</t>
-  </si>
-  <si>
-    <t>Paginated display list</t>
-  </si>
-  <si>
-    <t>As a TA / MO / Admin, I want to see pagination when there is too much list data so that I can improve the browsing experience.</t>
-  </si>
-  <si>
-    <t>1. Job list, applicant list, and application record list are paginated
-2. Each page displays a fixed amount of data and supports page turning operations
-3. Pagination navigation is clear and easy to use</t>
-  </si>
-  <si>
-    <t>P1-012</t>
-  </si>
-  <si>
-    <t>Key operation logs</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to record key actions and be able to view logs so that I can trace back to the history of operations.</t>
-  </si>
-  <si>
-    <t>1. Record the posting of positions, submitting applications, reviewing applications, account logins, etc
-2. The logs are stored as text files
-3. Administrators can view the log contents</t>
-  </si>
-  <si>
-    <t>P1-013</t>
-  </si>
-  <si>
-    <t>View individual application history</t>
-  </si>
-  <si>
-    <t>As a TA, I want to sift through all my application records by time so that I can review my application history.</t>
-  </si>
-  <si>
-    <t>1. The application record page supports filtering by time
-2. Display all application records (including withdrawn and unsuccessful)
-3. The list is updated in real time after filtering</t>
-  </si>
-  <si>
-    <t>P2-001</t>
-  </si>
-  <si>
-    <t>Collect the intended position</t>
-  </si>
-  <si>
-    <t>As a TA, I want to save the positions I am interested in so that I can quickly view and apply for them later.</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>P2-016</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Resume can be sent</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>As a MO, I want to see the resume uploaded by TA so that I can gain a better understanding of their personal abilities</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>P2</t>
-  </si>
-  <si>
-    <t>1. TAs can click the Favorite button on the job list/details page
-2. Favorite positions are displayed separately on the collection list page
-3. You can cancel your collection</t>
-  </si>
-  <si>
-    <t>P2-002</t>
-  </si>
-  <si>
-    <t>Local alerts on application status</t>
-  </si>
-  <si>
-    <t>As a TA, I want to be alerted when my application status changes so that I can stay up to date with the outcome of my application.</t>
-  </si>
-  <si>
-    <t>1. If the application status changes after logging in, a pop-up message will appear
-2. The prompt content includes the job title and status change results
-3. Prompts can be turned off</t>
-  </si>
-  <si>
-    <t>Local prompts, no SMS/email push</t>
-  </si>
-  <si>
-    <t>P2-003</t>
-  </si>
-  <si>
-    <t>File information export</t>
-  </si>
-  <si>
-    <t>As a TA, I want to export my file information to JSON format so that I can backup offline.</t>
-  </si>
-  <si>
-    <t>1. TAs can click the export button on the profile page
-2. The export file is in JSON format and contains all the archive information
-3. The exported file can be opened and viewed normally</t>
-  </si>
-  <si>
-    <t>Whether to choose JSON format is to be discussed</t>
-  </si>
-  <si>
-    <t>P2-004</t>
-  </si>
-  <si>
-    <t>Set job skill requirements</t>
-  </si>
-  <si>
-    <t>As a MO, I want to add specific skill requirements when posting a job so that I can match hiring needs procisely.</t>
-  </si>
-  <si>
-    <t>1. You can add a skill requirement field to the job posting page
-2. Skill requirements can be selected or entered
-3. Skill requirements are displayed on the job details page</t>
-  </si>
-  <si>
-    <t>P2-005</t>
-  </si>
-  <si>
-    <t>Add review comments</t>
-  </si>
-  <si>
-    <t>As a MO, I want to fill out a comment at the time of review so that I can explain the reason for the review to the TA.</t>
-  </si>
-  <si>
-    <t>1. You can enter text comments during the review
-2. Comments are synchronized to the applicant's application record details page
-3. There is a limit to the length of the comment (e.g. up to 200 words).</t>
-  </si>
-  <si>
-    <t>P2-006</t>
-  </si>
-  <si>
-    <t>The job cut-off time will be automatically removed from the shelves</t>
-  </si>
-  <si>
-    <t>As a MO, I want positions to be automatically removed when the deadline is reached so that I don't receive late applications.</t>
-  </si>
-  <si>
-    <t>1. Positions that have reached the application deadline will be automatically removed
-2. After removal, it will be hidden from the public list and new applications cannot be submitted
-3. Submitted applications can still be reviewed</t>
-  </si>
-  <si>
-    <t>P2-007</t>
-  </si>
-  <si>
-    <t>View the TA Job Fundamentals information</t>
-  </si>
-  <si>
-    <t>As a MO, I want to look at TAs' past teaching assistant experiences so that it can help me assist in review decisions.</t>
-  </si>
-  <si>
-    <t>1. TA profiles include past employment fields
-2. The MO can view this information at the time of the review
-3. Clear information presentation</t>
-  </si>
-  <si>
-    <t>P2-008</t>
-  </si>
-  <si>
-    <t>Workload threshold alerts</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to set TA workload thresholds so that I can be alerted when TA is overloaded.</t>
-  </si>
-  <si>
-    <t>1. Administrators can set thresholds (e.g. up to 3 positions in a single semester)
-2. When the number of TA positions approaches/exceeds the threshold, the system will give a text warning
-3. Alerts are displayed on the Workload page</t>
-  </si>
-  <si>
-    <t>P2-009</t>
-  </si>
-  <si>
-    <t>Statistics of recruitment data of the whole hospital</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to count the recruitment data of the whole college so that I can assist the college management decision-making.</t>
-  </si>
-  <si>
-    <t>1. Statistics on the recruitment completion rate, TA job distribution, and recruitment progress of each MO for each course/activity
-2. Present in a table
-3. Accurate and real-time data statistics</t>
-  </si>
-  <si>
-    <t>P2-010</t>
-  </si>
-  <si>
-    <t>Global data export</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to export the core data of the whole hospital to CSV format so that it can be analysed offline.</t>
-  </si>
-  <si>
-    <t>1. Administrators can export job information, TA job information, and recruitment statistics
-2. Export the file in CSV format
-3. The exported file can be opened and viewed normally</t>
-  </si>
-  <si>
-    <t>Export format TBD</t>
-  </si>
-  <si>
-    <t>P2-011</t>
-  </si>
-  <si>
-    <t>Basic control of operation permissions</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to restrict the MO from only operating the posts I post so that I can ensure data security.</t>
-  </si>
-  <si>
-    <t>1. MO can only view/operate the posts posted by the MO
-2. It is prohibited to view/review applicants for other MO positions across accounts
-3. Permission verification is performed before operation</t>
-  </si>
-  <si>
-    <t>P2-012</t>
-  </si>
-  <si>
-    <t>Manually backup and restore data</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to manually back up and restore system data so that data loss is prevented.</t>
-  </si>
-  <si>
-    <t>1. Administrators can back up all system data (users, positions, application records)
-2. The backup file can be restored to the system
-3. There are clear prompts for backup/restore operations</t>
-  </si>
-  <si>
-    <t>P2-013</t>
-  </si>
-  <si>
-    <t>Interface interaction optimization</t>
-  </si>
-  <si>
-    <t>As a TA / MO / Admin, I want to use a more user-friendly interface so that it can improve the user experience.</t>
-  </si>
-  <si>
-    <t>1. Improve the interface navigation, pop-up prompts, and operation button layout
-2. The interface complies with the medium-fidelity prototype standard
-3. Smoother operation process</t>
-  </si>
-  <si>
-    <t>P2-014</t>
-  </si>
-  <si>
-    <t>Bilingual interface in Chinese and English</t>
-  </si>
-  <si>
-    <t>As a TA / MO / Admin, I want to switch between Chinese and English interfaces so that it can adapt to international usage scenarios.</t>
-  </si>
-  <si>
-    <t>1. The system supports switching between Chinese and English interfaces
-2. The core text is bilingual
-3. The interface is updated in real time after switching</t>
-  </si>
-  <si>
-    <t>P2-015</t>
-  </si>
-  <si>
-    <t>Job time reminder</t>
-  </si>
-  <si>
-    <t>As a TA, I want to see a deadline reminder when I check a position so that I can apply in time.</t>
-  </si>
-  <si>
-    <t>1. Positions marked with "Coming soon" &lt; 24 hours from the deadline
-2. Closed positions marked as "Not Applicable"
-3. The reminder sign is clearly visible</t>
-  </si>
-  <si>
-    <t>P2-016</t>
-  </si>
-  <si>
-    <t>Export the list of TAs</t>
-  </si>
-  <si>
-    <t>As a MO, I want to export the applicant information for this position in Excel format so that it can be viewed and statisticed offline offline.</t>
-  </si>
-  <si>
-    <t>1. MO can be clicked on the export button on the applicant list page
-2. The export file is in Excel format and contains the TA's core information
-3. The exported file can be opened and viewed normally</t>
-  </si>
-  <si>
-    <t>P3-001</t>
-  </si>
-  <si>
-    <t>Tips on the matching degree of personal skills and positions</t>
-  </si>
-  <si>
-    <t>As a TA, I want to see a score on how well my skills match the position so that it can assist in job selection.</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>1. Job details page display match score (percentage)
-2. Scoring is calculated based on the TA's skills and job skills
-3. The scoring logic is explainable</t>
-  </si>
-  <si>
-    <t>AI value-added functions, optionally implemented</t>
-  </si>
-  <si>
-    <t>P3-002</t>
-  </si>
-  <si>
-    <t>Skill shortcomings identification tips</t>
-  </si>
-  <si>
-    <t>As a TA, I want to see my skills shortcomings and suggestions for improvement after applying, so that I can improve my abilities in a targeted manner.</t>
-  </si>
-  <si>
-    <t>1. After applying, the system compares the job requirements and points out the missing skills
-2. Give suggestions for basic improvement
-3. The prompt content is clear and easy to understand</t>
-  </si>
-  <si>
-    <t>P3-003</t>
-  </si>
-  <si>
-    <t>Intelligent screening of TA skills</t>
-  </si>
-  <si>
-    <t>As a MO, I want the system to automatically screen and prioritize high-match TAs so that it can improve screening efficiency.</t>
-  </si>
-  <si>
-    <t>1. The list of TAs is sorted by match, and high matching is prioritized
-2. The matching degree is calculated based on the job skill requirements
-3. Manually adjust the sorting</t>
-  </si>
-  <si>
-    <t>P3-004</t>
-  </si>
-  <si>
-    <t>Resume keyword extraction</t>
-  </si>
-  <si>
-    <t>As a MO, I want the system to automatically extract resume core keywords so that I can quickly understand TA competencies.</t>
-  </si>
-  <si>
-    <t>1. The system extracts key words such as core skills and work experience from the resume
-2. Keywords are displayed on the applicant's information page
-3. The extraction results can be manually verified</t>
-  </si>
-  <si>
-    <t>P3-005</t>
-  </si>
-  <si>
-    <t>TA workload equalization recommendation</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to get recommendations for optimizing TA assignments so that it can balance my workload.</t>
-  </si>
-  <si>
-    <t>1. The system gives an allocation recommendation based on the current TA load
-2. Suggestions can be viewed and modified manually
-3. Suggest logic that is explainable</t>
-  </si>
-  <si>
-    <t>P3-006</t>
-  </si>
-  <si>
-    <t>Intelligent statistics of recruitment demand</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to get reference recommendations for the number of TA recruitments for each course/activity to assist in planning.</t>
-  </si>
-  <si>
-    <t>1. Give a reference to the number of recruits based on past data
-2. References can be adjusted manually
-3. Statistical logic is explainable</t>
-  </si>
-  <si>
-    <t>P3-007</t>
-  </si>
-  <si>
-    <t>AI matching logic is configurable</t>
-  </si>
-  <si>
-    <t>As a Admin, I want to adjust the weight of job skill matching so that I can make the matching results more relevant to my actual needs.</t>
-  </si>
-  <si>
-    <t>1. Weights such as professional skills and work experience can be configured
-2. The matching calculation is updated in real time after configuration
-3. The configuration interface is clear and easy to use</t>
-  </si>
-  <si>
-    <t>P3-008</t>
-  </si>
-  <si>
-    <t>AI results are manually verified</t>
-  </si>
-  <si>
-    <t>As a system user, I want to validate AI-generated results so that I can avoid logical errors.</t>
-  </si>
-  <si>
-    <t>1. All AI-generated results support human viewing
-2. AI results can be modified manually
-3. The modified result overlays the AI-generated content</t>
-  </si>
-  <si>
-    <t>Uncertain</t>
-  </si>
-  <si>
-    <t>Core data persistence</t>
-  </si>
-  <si>
-    <t>As a system developer, I want to add and delete user files, job information, and application records, and store them persistently to ensure that data is not lost.</t>
-  </si>
-  <si>
-    <t>1. All user files, job information, and application records can be added, deleted, modified, and checked
-2. The data is stored in JSON format
-3. Data reading and writing without abnormalities</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. The TA can submit their resume along with the application
+2. MO can view the resume uploaded by TA in the application interface</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -854,151 +877,27 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="18"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1053,194 +952,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1276,253 +989,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1619,200 +1090,189 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
       <font>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <family val="2"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
     <dxf>
       <font>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <family val="2"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="18"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" wrapText="1"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="11"/>
+        <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+        <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </dxf>
     <dxf>
       <font>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <family val="2"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="11"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
         <name val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
         <scheme val="none"/>
-        <charset val="134"/>
-        <family val="2"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="18"/>
       </font>
       <alignment horizontal="center" vertical="center"/>
     </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <family val="2"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <family val="2"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <alignment vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <family val="2"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="center" vertical="center"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <family val="2"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <family val="2"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="微软雅黑"/>
-        <scheme val="none"/>
-        <charset val="134"/>
-        <family val="2"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="11"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF0F8FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ProductBacklogTable" displayName="ProductBacklogTable" ref="A1:J50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="ProductBacklogTable" displayName="ProductBacklogTable" ref="A1:J51">
   <tableColumns count="10">
-    <tableColumn id="1" name="Story ID" dataDxfId="0"/>
-    <tableColumn id="2" name="Story Name" dataDxfId="1"/>
-    <tableColumn id="3" name="Description" dataDxfId="2"/>
-    <tableColumn id="4" name="Priority" dataDxfId="3"/>
-    <tableColumn id="5" name="Iteration (Sprint) number" dataDxfId="4"/>
-    <tableColumn id="6" name="Acceptance Criteria" dataDxfId="5"/>
-    <tableColumn id="7" name="Estimation/day" dataDxfId="6"/>
-    <tableColumn id="8" name="Notes" dataDxfId="7"/>
-    <tableColumn id="9" name="Date started (or planned)" dataDxfId="8"/>
-    <tableColumn id="10" name="Date finished (or planned)" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Story ID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Story Name" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Priority" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Iteration (Sprint) number" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Acceptance Criteria" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Estimation/day" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Notes" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Date started (or planned)" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Date finished (or planned)" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2097,28 +1557,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="23"/>
+  <dimension ref="A1:J52"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="22.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.2181818181818" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" style="3" customWidth="1"/>
     <col min="2" max="2" width="44" style="4" customWidth="1"/>
-    <col min="3" max="3" width="43.4454545454545" style="5" customWidth="1"/>
-    <col min="4" max="4" width="11.2181818181818" style="6" customWidth="1"/>
-    <col min="5" max="5" width="33.4454545454545" style="3" customWidth="1"/>
-    <col min="6" max="6" width="60.7818181818182" style="5" customWidth="1"/>
-    <col min="7" max="7" width="19.1090909090909" style="3" customWidth="1"/>
-    <col min="8" max="8" width="29.2181818181818" style="4" customWidth="1"/>
-    <col min="9" max="9" width="33.4454545454545" customWidth="1"/>
-    <col min="10" max="10" width="34.7818181818182" customWidth="1"/>
+    <col min="3" max="3" width="43.44140625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="33.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="60.77734375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="19.109375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="29.21875" style="4" customWidth="1"/>
+    <col min="9" max="9" width="33.44140625" customWidth="1"/>
+    <col min="10" max="10" width="34.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="45" customHeight="1" spans="1:10">
+    <row r="1" spans="1:10" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2150,7 +1611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="130.05" customHeight="1" spans="1:10">
+    <row r="2" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>10</v>
       </c>
@@ -2178,7 +1639,7 @@
       <c r="I2" s="13"/>
       <c r="J2" s="13"/>
     </row>
-    <row r="3" ht="130.05" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>16</v>
       </c>
@@ -2204,7 +1665,7 @@
       <c r="I3" s="18"/>
       <c r="J3" s="18"/>
     </row>
-    <row r="4" ht="167.4" customHeight="1" spans="1:10">
+    <row r="4" spans="1:10" ht="167.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19" t="s">
         <v>20</v>
       </c>
@@ -2230,7 +1691,7 @@
       <c r="I4" s="22"/>
       <c r="J4" s="22"/>
     </row>
-    <row r="5" ht="130.05" customHeight="1" spans="1:10">
+    <row r="5" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>24</v>
       </c>
@@ -2256,7 +1717,7 @@
       <c r="I5" s="18"/>
       <c r="J5" s="18"/>
     </row>
-    <row r="6" ht="130.05" customHeight="1" spans="1:10">
+    <row r="6" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19" t="s">
         <v>28</v>
       </c>
@@ -2282,7 +1743,7 @@
       <c r="I6" s="22"/>
       <c r="J6" s="22"/>
     </row>
-    <row r="7" ht="130.05" customHeight="1" spans="1:10">
+    <row r="7" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>32</v>
       </c>
@@ -2308,7 +1769,7 @@
       <c r="I7" s="18"/>
       <c r="J7" s="18"/>
     </row>
-    <row r="8" ht="130.05" customHeight="1" spans="1:10">
+    <row r="8" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19" t="s">
         <v>36</v>
       </c>
@@ -2334,7 +1795,7 @@
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
     </row>
-    <row r="9" ht="165" customHeight="1" spans="1:10">
+    <row r="9" spans="1:10" ht="165" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>40</v>
       </c>
@@ -2360,7 +1821,7 @@
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
     </row>
-    <row r="10" ht="130.05" customHeight="1" spans="1:10">
+    <row r="10" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>44</v>
       </c>
@@ -2386,7 +1847,7 @@
       <c r="I10" s="22"/>
       <c r="J10" s="22"/>
     </row>
-    <row r="11" ht="130.05" customHeight="1" spans="1:10">
+    <row r="11" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>48</v>
       </c>
@@ -2414,7 +1875,7 @@
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
     </row>
-    <row r="12" ht="130.2" customHeight="1" spans="1:10">
+    <row r="12" spans="1:10" ht="130.19999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19" t="s">
         <v>53</v>
       </c>
@@ -2440,7 +1901,7 @@
       <c r="I12" s="22"/>
       <c r="J12" s="22"/>
     </row>
-    <row r="13" ht="130.05" customHeight="1" spans="1:10">
+    <row r="13" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>57</v>
       </c>
@@ -2466,7 +1927,7 @@
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
     </row>
-    <row r="14" ht="130.05" customHeight="1" spans="1:10">
+    <row r="14" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="19" t="s">
         <v>61</v>
       </c>
@@ -2492,7 +1953,7 @@
       <c r="I14" s="22"/>
       <c r="J14" s="22"/>
     </row>
-    <row r="15" ht="130.05" customHeight="1" spans="1:10">
+    <row r="15" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>66</v>
       </c>
@@ -2518,7 +1979,7 @@
       <c r="I15" s="18"/>
       <c r="J15" s="18"/>
     </row>
-    <row r="16" ht="130.05" customHeight="1" spans="1:10">
+    <row r="16" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19" t="s">
         <v>70</v>
       </c>
@@ -2534,27 +1995,27 @@
       <c r="E16" s="19">
         <v>2</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="G16" s="19">
+        <v>2</v>
+      </c>
+      <c r="H16" s="20" t="s">
         <v>73</v>
-      </c>
-      <c r="G16" s="19">
-        <v>2</v>
-      </c>
-      <c r="H16" s="20" t="s">
-        <v>74</v>
       </c>
       <c r="I16" s="22"/>
       <c r="J16" s="22"/>
     </row>
-    <row r="17" ht="130.05" customHeight="1" spans="1:10">
+    <row r="17" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>76</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>77</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>64</v>
@@ -2563,7 +2024,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G17" s="14">
         <v>1</v>
@@ -2572,15 +2033,15 @@
       <c r="I17" s="18"/>
       <c r="J17" s="18"/>
     </row>
-    <row r="18" ht="130.05" customHeight="1" spans="1:10">
+    <row r="18" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="C18" s="28" t="s">
         <v>80</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>81</v>
       </c>
       <c r="D18" s="26" t="s">
         <v>64</v>
@@ -2589,7 +2050,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G18" s="19">
         <v>2</v>
@@ -2598,15 +2059,15 @@
       <c r="I18" s="22"/>
       <c r="J18" s="22"/>
     </row>
-    <row r="19" ht="130.05" customHeight="1" spans="1:10">
+    <row r="19" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>84</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>85</v>
       </c>
       <c r="D19" s="26" t="s">
         <v>64</v>
@@ -2615,7 +2076,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G19" s="14">
         <v>1</v>
@@ -2624,15 +2085,15 @@
       <c r="I19" s="18"/>
       <c r="J19" s="18"/>
     </row>
-    <row r="20" ht="130.05" customHeight="1" spans="1:10">
+    <row r="20" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="C20" s="21" t="s">
         <v>88</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>89</v>
       </c>
       <c r="D20" s="26" t="s">
         <v>64</v>
@@ -2641,7 +2102,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="21" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G20" s="19">
         <v>2</v>
@@ -2650,15 +2111,15 @@
       <c r="I20" s="22"/>
       <c r="J20" s="22"/>
     </row>
-    <row r="21" ht="130.05" customHeight="1" spans="1:10">
+    <row r="21" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="C21" s="16" t="s">
         <v>92</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="D21" s="26" t="s">
         <v>64</v>
@@ -2667,7 +2128,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G21" s="14">
         <v>2</v>
@@ -2676,15 +2137,15 @@
       <c r="I21" s="18"/>
       <c r="J21" s="18"/>
     </row>
-    <row r="22" ht="130.05" customHeight="1" spans="1:10">
+    <row r="22" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="C22" s="28" t="s">
         <v>96</v>
-      </c>
-      <c r="C22" s="28" t="s">
-        <v>97</v>
       </c>
       <c r="D22" s="26" t="s">
         <v>64</v>
@@ -2693,7 +2154,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G22" s="19">
         <v>2</v>
@@ -2702,15 +2163,15 @@
       <c r="I22" s="22"/>
       <c r="J22" s="22"/>
     </row>
-    <row r="23" ht="130.05" customHeight="1" spans="1:10">
+    <row r="23" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="C23" s="16" t="s">
         <v>100</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>101</v>
       </c>
       <c r="D23" s="26" t="s">
         <v>64</v>
@@ -2719,7 +2180,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G23" s="14">
         <v>1</v>
@@ -2728,15 +2189,15 @@
       <c r="I23" s="18"/>
       <c r="J23" s="18"/>
     </row>
-    <row r="24" ht="130.05" customHeight="1" spans="1:10">
+    <row r="24" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="C24" s="28" t="s">
         <v>104</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>105</v>
       </c>
       <c r="D24" s="26" t="s">
         <v>64</v>
@@ -2745,7 +2206,7 @@
         <v>2</v>
       </c>
       <c r="F24" s="21" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G24" s="19">
         <v>2</v>
@@ -2754,15 +2215,15 @@
       <c r="I24" s="22"/>
       <c r="J24" s="22"/>
     </row>
-    <row r="25" ht="130.05" customHeight="1" spans="1:10">
+    <row r="25" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="C25" s="16" t="s">
         <v>108</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>109</v>
       </c>
       <c r="D25" s="26" t="s">
         <v>64</v>
@@ -2770,8 +2231,8 @@
       <c r="E25" s="14">
         <v>2</v>
       </c>
-      <c r="F25" s="16" t="s">
-        <v>110</v>
+      <c r="F25" s="36" t="s">
+        <v>219</v>
       </c>
       <c r="G25" s="14">
         <v>2</v>
@@ -2780,15 +2241,15 @@
       <c r="I25" s="18"/>
       <c r="J25" s="18"/>
     </row>
-    <row r="26" ht="130.05" customHeight="1" spans="1:10">
+    <row r="26" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>111</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>113</v>
       </c>
       <c r="D26" s="26" t="s">
         <v>64</v>
@@ -2797,7 +2258,7 @@
         <v>2</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G26" s="19">
         <v>1</v>
@@ -2806,24 +2267,24 @@
       <c r="I26" s="22"/>
       <c r="J26" s="22"/>
     </row>
-    <row r="27" ht="130.05" customHeight="1" spans="1:10">
+    <row r="27" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C27" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="D27" s="29" t="s">
         <v>116</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="D27" s="29" t="s">
-        <v>118</v>
       </c>
       <c r="E27" s="14">
         <v>3</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
@@ -2832,80 +2293,80 @@
       <c r="I27" s="18"/>
       <c r="J27" s="18"/>
     </row>
-    <row r="28" ht="130.05" customHeight="1" spans="1:10">
+    <row r="28" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="B28" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>122</v>
-      </c>
       <c r="D28" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E28" s="19">
         <v>3</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G28" s="19">
         <v>2</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I28" s="22"/>
       <c r="J28" s="22"/>
     </row>
-    <row r="29" ht="130.05" customHeight="1" spans="1:10">
+    <row r="29" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="C29" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="B29" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>127</v>
-      </c>
       <c r="D29" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E29" s="14">
         <v>3</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G29" s="14">
         <v>2</v>
       </c>
       <c r="H29" s="15" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I29" s="18"/>
       <c r="J29" s="18"/>
     </row>
-    <row r="30" ht="130.05" customHeight="1" spans="1:10">
+    <row r="30" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="B30" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>132</v>
-      </c>
       <c r="D30" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E30" s="19">
         <v>3</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G30" s="19">
         <v>2</v>
@@ -2914,24 +2375,24 @@
       <c r="I30" s="22"/>
       <c r="J30" s="22"/>
     </row>
-    <row r="31" ht="130.05" customHeight="1" spans="1:10">
+    <row r="31" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="C31" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>136</v>
-      </c>
       <c r="D31" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E31" s="14">
         <v>3</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
@@ -2940,24 +2401,24 @@
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
     </row>
-    <row r="32" ht="130.05" customHeight="1" spans="1:10">
+    <row r="32" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="B32" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>140</v>
-      </c>
       <c r="D32" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E32" s="19">
         <v>3</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G32" s="19">
         <v>1</v>
@@ -2966,24 +2427,24 @@
       <c r="I32" s="22"/>
       <c r="J32" s="22"/>
     </row>
-    <row r="33" ht="130.05" customHeight="1" spans="1:10">
+    <row r="33" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="B33" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>144</v>
-      </c>
       <c r="D33" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E33" s="14">
         <v>3</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="G33" s="14">
         <v>2</v>
@@ -2992,24 +2453,24 @@
       <c r="I33" s="18"/>
       <c r="J33" s="18"/>
     </row>
-    <row r="34" ht="130.05" customHeight="1" spans="1:10">
+    <row r="34" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="B34" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>148</v>
-      </c>
       <c r="D34" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E34" s="19">
         <v>3</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G34" s="19">
         <v>2</v>
@@ -3018,24 +2479,24 @@
       <c r="I34" s="22"/>
       <c r="J34" s="22"/>
     </row>
-    <row r="35" ht="130.05" customHeight="1" spans="1:10">
+    <row r="35" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C35" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="C35" s="16" t="s">
-        <v>152</v>
-      </c>
       <c r="D35" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E35" s="14">
         <v>3</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G35" s="14">
         <v>1</v>
@@ -3044,52 +2505,52 @@
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
     </row>
-    <row r="36" ht="130.05" customHeight="1" spans="1:10">
+    <row r="36" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="B36" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>156</v>
-      </c>
       <c r="D36" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E36" s="19">
         <v>3</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G36" s="19">
         <v>2</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="I36" s="22"/>
       <c r="J36" s="22"/>
     </row>
-    <row r="37" ht="130.05" customHeight="1" spans="1:10">
+    <row r="37" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="C37" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="B37" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C37" s="16" t="s">
-        <v>161</v>
-      </c>
       <c r="D37" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E37" s="14">
         <v>3</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G37" s="14">
         <v>1</v>
@@ -3098,24 +2559,24 @@
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
     </row>
-    <row r="38" ht="130.05" customHeight="1" spans="1:10">
+    <row r="38" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="B38" s="20" t="s">
-        <v>164</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>165</v>
-      </c>
       <c r="D38" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E38" s="19">
         <v>3</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G38" s="19">
         <v>2</v>
@@ -3124,24 +2585,24 @@
       <c r="I38" s="22"/>
       <c r="J38" s="22"/>
     </row>
-    <row r="39" ht="130.05" customHeight="1" spans="1:10">
+    <row r="39" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="B39" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="C39" s="16" t="s">
-        <v>169</v>
-      </c>
       <c r="D39" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E39" s="14">
         <v>3</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G39" s="14">
         <v>2</v>
@@ -3150,24 +2611,24 @@
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
     </row>
-    <row r="40" ht="130.05" customHeight="1" spans="1:10">
+    <row r="40" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="B40" s="20" t="s">
-        <v>172</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>173</v>
-      </c>
       <c r="D40" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E40" s="19">
         <v>3</v>
       </c>
       <c r="F40" s="21" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G40" s="19">
         <v>1</v>
@@ -3176,24 +2637,24 @@
       <c r="I40" s="22"/>
       <c r="J40" s="22"/>
     </row>
-    <row r="41" ht="130.05" customHeight="1" spans="1:10">
+    <row r="41" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="C41" s="16" t="s">
         <v>175</v>
       </c>
-      <c r="B41" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="C41" s="16" t="s">
-        <v>177</v>
-      </c>
       <c r="D41" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E41" s="14">
         <v>3</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G41" s="14">
         <v>2</v>
@@ -3202,24 +2663,24 @@
       <c r="I41" s="18"/>
       <c r="J41" s="18"/>
     </row>
-    <row r="42" ht="130.05" customHeight="1" spans="1:10">
+    <row r="42" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>178</v>
+      </c>
+      <c r="C42" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="B42" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="C42" s="21" t="s">
-        <v>181</v>
-      </c>
       <c r="D42" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E42" s="19">
         <v>3</v>
       </c>
       <c r="F42" s="21" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G42" s="19">
         <v>1</v>
@@ -3228,239 +2689,265 @@
       <c r="I42" s="22"/>
       <c r="J42" s="22"/>
     </row>
-    <row r="43" ht="130.05" customHeight="1" spans="1:10">
-      <c r="A43" s="14" t="s">
+    <row r="43" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="39" t="s">
+        <v>221</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>222</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>223</v>
+      </c>
+      <c r="D43" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="E43" s="39">
+        <v>3</v>
+      </c>
+      <c r="F43" s="41" t="s">
+        <v>225</v>
+      </c>
+      <c r="G43" s="39">
+        <v>1</v>
+      </c>
+      <c r="H43" s="40"/>
+      <c r="I43" s="42"/>
+      <c r="J43" s="42"/>
+    </row>
+    <row r="44" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="D44" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="E44" s="14">
+        <v>4</v>
+      </c>
+      <c r="F44" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="D43" s="30" t="s">
+      <c r="G44" s="14">
+        <v>2</v>
+      </c>
+      <c r="H44" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="E43" s="14">
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+    </row>
+    <row r="45" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="43" t="s">
+        <v>187</v>
+      </c>
+      <c r="B45" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="D45" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E45" s="43">
         <v>4</v>
       </c>
-      <c r="F43" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="G43" s="14">
-        <v>2</v>
-      </c>
-      <c r="H43" s="15" t="s">
-        <v>188</v>
-      </c>
-      <c r="I43" s="18"/>
-      <c r="J43" s="18"/>
-    </row>
-    <row r="44" ht="130.05" customHeight="1" spans="1:10">
-      <c r="A44" s="19" t="s">
-        <v>189</v>
-      </c>
-      <c r="B44" s="20" t="s">
+      <c r="F45" s="45" t="s">
         <v>190</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="G45" s="43">
+        <v>1</v>
+      </c>
+      <c r="H45" s="44"/>
+      <c r="I45" s="46"/>
+      <c r="J45" s="46"/>
+    </row>
+    <row r="46" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="D44" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="E44" s="19">
+      <c r="B46" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="D46" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E46" s="14">
         <v>4</v>
       </c>
-      <c r="F44" s="21" t="s">
-        <v>192</v>
-      </c>
-      <c r="G44" s="19">
-        <v>1</v>
-      </c>
-      <c r="H44" s="20"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
-    </row>
-    <row r="45" ht="130.05" customHeight="1" spans="1:10">
-      <c r="A45" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="B45" s="15" t="s">
+      <c r="F46" s="16" t="s">
         <v>194</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="G46" s="14">
+        <v>1</v>
+      </c>
+      <c r="H46" s="15"/>
+      <c r="I46" s="18"/>
+      <c r="J46" s="18"/>
+    </row>
+    <row r="47" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="43" t="s">
         <v>195</v>
       </c>
-      <c r="D45" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="E45" s="14">
+      <c r="B47" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="C47" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="D47" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E47" s="43">
         <v>4</v>
       </c>
-      <c r="F45" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="G45" s="14">
-        <v>1</v>
-      </c>
-      <c r="H45" s="15"/>
-      <c r="I45" s="18"/>
-      <c r="J45" s="18"/>
-    </row>
-    <row r="46" ht="130.05" customHeight="1" spans="1:10">
-      <c r="A46" s="19" t="s">
-        <v>197</v>
-      </c>
-      <c r="B46" s="20" t="s">
+      <c r="F47" s="45" t="s">
         <v>198</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="G47" s="43">
+        <v>2</v>
+      </c>
+      <c r="H47" s="44"/>
+      <c r="I47" s="46"/>
+      <c r="J47" s="46"/>
+    </row>
+    <row r="48" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="D46" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="E46" s="19">
+      <c r="B48" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="D48" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E48" s="14">
         <v>4</v>
       </c>
-      <c r="F46" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="G46" s="19">
-        <v>2</v>
-      </c>
-      <c r="H46" s="20"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-    </row>
-    <row r="47" ht="130.05" customHeight="1" spans="1:10">
-      <c r="A47" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="B47" s="15" t="s">
+      <c r="F48" s="16" t="s">
         <v>202</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="G48" s="14">
+        <v>1</v>
+      </c>
+      <c r="H48" s="15"/>
+      <c r="I48" s="18"/>
+      <c r="J48" s="18"/>
+    </row>
+    <row r="49" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="43" t="s">
         <v>203</v>
       </c>
-      <c r="D47" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="E47" s="14">
+      <c r="B49" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="C49" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="D49" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E49" s="43">
         <v>4</v>
       </c>
-      <c r="F47" s="16" t="s">
-        <v>204</v>
-      </c>
-      <c r="G47" s="14">
-        <v>1</v>
-      </c>
-      <c r="H47" s="15"/>
-      <c r="I47" s="18"/>
-      <c r="J47" s="18"/>
-    </row>
-    <row r="48" ht="130.05" customHeight="1" spans="1:10">
-      <c r="A48" s="19" t="s">
-        <v>205</v>
-      </c>
-      <c r="B48" s="20" t="s">
+      <c r="F49" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="G49" s="43">
+        <v>2</v>
+      </c>
+      <c r="H49" s="44"/>
+      <c r="I49" s="46"/>
+      <c r="J49" s="46"/>
+    </row>
+    <row r="50" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="D48" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="E48" s="19">
+      <c r="B50" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="D50" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E50" s="14">
         <v>4</v>
       </c>
-      <c r="F48" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="G48" s="19">
-        <v>2</v>
-      </c>
-      <c r="H48" s="20"/>
-      <c r="I48" s="22"/>
-      <c r="J48" s="22"/>
-    </row>
-    <row r="49" ht="130.05" customHeight="1" spans="1:10">
-      <c r="A49" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="B49" s="15" t="s">
+      <c r="F50" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="G50" s="14">
+        <v>2</v>
+      </c>
+      <c r="H50" s="15"/>
+      <c r="I50" s="18"/>
+      <c r="J50" s="18"/>
+    </row>
+    <row r="51" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="D49" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="E49" s="14">
+      <c r="B51" s="44" t="s">
+        <v>212</v>
+      </c>
+      <c r="C51" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="D51" s="30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E51" s="43">
         <v>4</v>
       </c>
-      <c r="F49" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="G49" s="14">
-        <v>2</v>
-      </c>
-      <c r="H49" s="15"/>
-      <c r="I49" s="18"/>
-      <c r="J49" s="18"/>
-    </row>
-    <row r="50" ht="130.05" customHeight="1" spans="1:10">
-      <c r="A50" s="19" t="s">
-        <v>213</v>
-      </c>
-      <c r="B50" s="20" t="s">
+      <c r="F51" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="G51" s="43">
+        <v>1</v>
+      </c>
+      <c r="H51" s="44"/>
+      <c r="I51" s="46"/>
+      <c r="J51" s="46"/>
+    </row>
+    <row r="52" spans="1:10" s="2" customFormat="1" ht="94.8" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="D50" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="E50" s="19">
-        <v>4</v>
-      </c>
-      <c r="F50" s="21" t="s">
+      <c r="B52" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="G50" s="19">
-        <v>1</v>
-      </c>
-      <c r="H50" s="20"/>
-      <c r="I50" s="22"/>
-      <c r="J50" s="22"/>
-    </row>
-    <row r="51" s="2" customFormat="1" ht="94.8" customHeight="1" spans="1:10">
-      <c r="A51" s="31" t="s">
+      <c r="C52" s="33" t="s">
         <v>217</v>
       </c>
-      <c r="B51" s="32" t="s">
+      <c r="D52" s="34"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="C51" s="33" t="s">
-        <v>219</v>
-      </c>
-      <c r="D51" s="34"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="G51" s="31"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="35"/>
-      <c r="J51" s="35"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/docs/Product_Backlog.xlsx
+++ b/docs/Product_Backlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\java项目\EBU6304-Group17\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0E093B-1ACC-48DA-A053-EFE4EDE76171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBCD1AB-1E0A-4ECD-A8BA-721446DDE501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2716,32 +2716,32 @@
       <c r="J43" s="42"/>
     </row>
     <row r="44" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="14" t="s">
+      <c r="A44" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="B44" s="15" t="s">
+      <c r="B44" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="21" t="s">
         <v>183</v>
       </c>
       <c r="D44" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="E44" s="14">
+      <c r="E44" s="19">
         <v>4</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="F44" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="G44" s="14">
-        <v>2</v>
-      </c>
-      <c r="H44" s="15" t="s">
+      <c r="G44" s="19">
+        <v>2</v>
+      </c>
+      <c r="H44" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="I44" s="18"/>
-      <c r="J44" s="18"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
     </row>
     <row r="45" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="43" t="s">
@@ -2770,30 +2770,30 @@
       <c r="J45" s="46"/>
     </row>
     <row r="46" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="B46" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="21" t="s">
         <v>193</v>
       </c>
       <c r="D46" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="E46" s="14">
+      <c r="E46" s="19">
         <v>4</v>
       </c>
-      <c r="F46" s="16" t="s">
+      <c r="F46" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="G46" s="14">
-        <v>1</v>
-      </c>
-      <c r="H46" s="15"/>
-      <c r="I46" s="18"/>
-      <c r="J46" s="18"/>
+      <c r="G46" s="19">
+        <v>1</v>
+      </c>
+      <c r="H46" s="20"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
     </row>
     <row r="47" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="43" t="s">
@@ -2822,30 +2822,30 @@
       <c r="J47" s="46"/>
     </row>
     <row r="48" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="14" t="s">
+      <c r="A48" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="B48" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="21" t="s">
         <v>201</v>
       </c>
       <c r="D48" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="E48" s="14">
+      <c r="E48" s="19">
         <v>4</v>
       </c>
-      <c r="F48" s="16" t="s">
+      <c r="F48" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="G48" s="14">
-        <v>1</v>
-      </c>
-      <c r="H48" s="15"/>
-      <c r="I48" s="18"/>
-      <c r="J48" s="18"/>
+      <c r="G48" s="19">
+        <v>1</v>
+      </c>
+      <c r="H48" s="20"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="22"/>
     </row>
     <row r="49" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="43" t="s">
@@ -2874,30 +2874,30 @@
       <c r="J49" s="46"/>
     </row>
     <row r="50" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="B50" s="15" t="s">
+      <c r="B50" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="21" t="s">
         <v>209</v>
       </c>
       <c r="D50" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="E50" s="14">
+      <c r="E50" s="19">
         <v>4</v>
       </c>
-      <c r="F50" s="16" t="s">
+      <c r="F50" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="G50" s="14">
-        <v>2</v>
-      </c>
-      <c r="H50" s="15"/>
-      <c r="I50" s="18"/>
-      <c r="J50" s="18"/>
+      <c r="G50" s="19">
+        <v>2</v>
+      </c>
+      <c r="H50" s="20"/>
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
     </row>
     <row r="51" spans="1:10" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="43" t="s">
